--- a/Ahmed_Ex3A_tables.xlsx
+++ b/Ahmed_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvieahmed\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6113E3E4-A6FA-46FD-A4CC-26F1C9755AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D908336D-38E7-42B4-A0E3-FA66F97181DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FC54A01-D4B9-4BC6-BD27-AE9C4836502D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{7FC54A01-D4B9-4BC6-BD27-AE9C4836502D}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="100">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -99,6 +99,249 @@
   </si>
   <si>
     <t>Payment_Status</t>
+  </si>
+  <si>
+    <t>Tom</t>
+  </si>
+  <si>
+    <t>Jerry</t>
+  </si>
+  <si>
+    <t>518-525-1101</t>
+  </si>
+  <si>
+    <t>tomjerry@gmail.com</t>
+  </si>
+  <si>
+    <t>Spike</t>
+  </si>
+  <si>
+    <t>Pitbull</t>
+  </si>
+  <si>
+    <t>Good luck</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>Olivia</t>
+  </si>
+  <si>
+    <t>Bennett</t>
+  </si>
+  <si>
+    <t>518-555-0102</t>
+  </si>
+  <si>
+    <t>olivia.bennett@example.com</t>
+  </si>
+  <si>
+    <t>Marcus</t>
+  </si>
+  <si>
+    <t>Lee</t>
+  </si>
+  <si>
+    <t>518-555-0103</t>
+  </si>
+  <si>
+    <t>marcus.lee@example.com</t>
+  </si>
+  <si>
+    <t>Sophia</t>
+  </si>
+  <si>
+    <t>Patel</t>
+  </si>
+  <si>
+    <t>518-555-0104</t>
+  </si>
+  <si>
+    <t>sophia.patel@example.com</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Brooks</t>
+  </si>
+  <si>
+    <t>518-555-0105</t>
+  </si>
+  <si>
+    <t>daniel.brooks@example.com</t>
+  </si>
+  <si>
+    <t>Ava</t>
+  </si>
+  <si>
+    <t>Martinez</t>
+  </si>
+  <si>
+    <t>518-555-0106</t>
+  </si>
+  <si>
+    <t>ava.martinez@example.com</t>
+  </si>
+  <si>
+    <t>Ethan</t>
+  </si>
+  <si>
+    <t>Carter</t>
+  </si>
+  <si>
+    <t>518-555-0107</t>
+  </si>
+  <si>
+    <t>ethan.carter@example.com</t>
+  </si>
+  <si>
+    <t>Mia</t>
+  </si>
+  <si>
+    <t>Robinson</t>
+  </si>
+  <si>
+    <t>518-555-0108</t>
+  </si>
+  <si>
+    <t>mia.robinson@example.com</t>
+  </si>
+  <si>
+    <t>Noah</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>518-555-0109</t>
+  </si>
+  <si>
+    <t>noah.thompson@example.com</t>
+  </si>
+  <si>
+    <t>Chloe</t>
+  </si>
+  <si>
+    <t>Nguyen</t>
+  </si>
+  <si>
+    <t>518-555-0110</t>
+  </si>
+  <si>
+    <t>chloe.nguyen@example.com</t>
+  </si>
+  <si>
+    <t>Liam</t>
+  </si>
+  <si>
+    <t>Foster</t>
+  </si>
+  <si>
+    <t>518-555-0111</t>
+  </si>
+  <si>
+    <t>liam.foster@example.com</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>Golden Retriever</t>
+  </si>
+  <si>
+    <t>Loves treats</t>
+  </si>
+  <si>
+    <t>Milo</t>
+  </si>
+  <si>
+    <t>Beagle</t>
+  </si>
+  <si>
+    <t>Keep on leash</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>Labrador Retriever</t>
+  </si>
+  <si>
+    <t>Avoid loud noises</t>
+  </si>
+  <si>
+    <t>Rocky</t>
+  </si>
+  <si>
+    <t>German Shepherd</t>
+  </si>
+  <si>
+    <t>Needs water breaks</t>
+  </si>
+  <si>
+    <t>Daisy</t>
+  </si>
+  <si>
+    <t>Poodle</t>
+  </si>
+  <si>
+    <t>Shy with strangers</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Bulldog</t>
+  </si>
+  <si>
+    <t>Short walks only</t>
+  </si>
+  <si>
+    <t>Coco</t>
+  </si>
+  <si>
+    <t>Shih Tzu</t>
+  </si>
+  <si>
+    <t>Avoid large dogs</t>
+  </si>
+  <si>
+    <t>Teddy</t>
+  </si>
+  <si>
+    <t>Corgi</t>
+  </si>
+  <si>
+    <t>Chases squirrels</t>
+  </si>
+  <si>
+    <t>Nala</t>
+  </si>
+  <si>
+    <t>Husky</t>
+  </si>
+  <si>
+    <t>Pulls on leash</t>
+  </si>
+  <si>
+    <t>Charlie</t>
+  </si>
+  <si>
+    <t>Boxer</t>
+  </si>
+  <si>
+    <t>Prefers quiet routes</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>Online</t>
   </si>
 </sst>
 </file>
@@ -146,10 +389,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,14 +730,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02EAA72-246A-4A19-958C-12A7DAE9220A}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="10.7265625" customWidth="1"/>
     <col min="4" max="4" width="13.90625" customWidth="1"/>
-    <col min="5" max="5" width="7.26953125" customWidth="1"/>
+    <col min="5" max="5" width="28.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -509,6 +755,193 @@
       </c>
       <c r="E1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -518,12 +951,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2E3C56B-446E-482F-8AD9-95A371A53DA7}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.08984375" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" customWidth="1"/>
+    <col min="6" max="6" width="20.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -544,6 +977,226 @@
       </c>
       <c r="F1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -553,11 +1206,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87714E16-9FD1-4B85-9D01-F145E9F14DE5}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="7.6328125" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" customWidth="1"/>
     <col min="5" max="5" width="9.81640625" customWidth="1"/>
   </cols>
@@ -579,6 +1232,193 @@
         <v>13</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>46320</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.39583333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46321</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.39583333333333331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46320</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3">
+        <v>46320</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46320</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46320</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46320</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46321</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46321</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46321</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3">
+        <v>46321</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0.625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -586,14 +1426,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE512214-7254-4028-865E-0DD4907931E2}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.54296875" customWidth="1"/>
     <col min="3" max="3" width="15.90625" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="9.08984375" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -616,6 +1456,226 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46320</v>
+      </c>
+      <c r="E2" s="5">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="3">
+        <v>46321</v>
+      </c>
+      <c r="E3">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46320</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46320</v>
+      </c>
+      <c r="E5">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46320</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46320</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46320</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46321</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46321</v>
+      </c>
+      <c r="E10">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46321</v>
+      </c>
+      <c r="E11">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="3">
+        <v>46321</v>
+      </c>
+      <c r="E12">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
